--- a/Config/Excel/language/lang_item.xlsx
+++ b/Config/Excel/language/lang_item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="9880"/>
+    <workbookView windowWidth="29865" windowHeight="12735"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
   <si>
     <t>text</t>
+  </si>
+  <si>
+    <t>color</t>
   </si>
   <si>
     <t>c</t>
@@ -1032,75 +1035,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="19.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="37.2545454545455" customWidth="1"/>
+    <col min="1" max="1" width="19.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="37.2583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>920001</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>920002</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>920003</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>920004</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1114,14 +1141,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1">
         <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1129,7 +1156,7 @@
         <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1143,7 +1170,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Excel/language/lang_item.xlsx
+++ b/Config/Excel/language/lang_item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\language\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A540FED-E986-47CF-B3A6-73A35FCA8FA0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38CD696-71BE-4C50-A688-6604848A8DDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="29865" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -64,6 +64,75 @@
   </si>
   <si>
     <t>药草</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_920001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_920002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_920003</t>
+  </si>
+  <si>
+    <t>item_920004</t>
+  </si>
+  <si>
+    <t>item_920005</t>
+  </si>
+  <si>
+    <t>item_920006</t>
+  </si>
+  <si>
+    <t>item_920007</t>
+  </si>
+  <si>
+    <t>item_920008</t>
+  </si>
+  <si>
+    <t>item_920009</t>
+  </si>
+  <si>
+    <t>item_920010</t>
+  </si>
+  <si>
+    <t>item_920011</t>
+  </si>
+  <si>
+    <t>item_920012</t>
+  </si>
+  <si>
+    <t>item_920013</t>
+  </si>
+  <si>
+    <t>item_920014</t>
+  </si>
+  <si>
+    <t>item_920015</t>
+  </si>
+  <si>
+    <t>item_920016</t>
+  </si>
+  <si>
+    <t>item_920017</t>
+  </si>
+  <si>
+    <t>item_920018</t>
+  </si>
+  <si>
+    <t>item_920019</t>
+  </si>
+  <si>
+    <t>item_920020</t>
+  </si>
+  <si>
+    <t>item_920021</t>
+  </si>
+  <si>
+    <t>string</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -458,8 +527,8 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>4</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -480,8 +549,8 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>920001</v>
+      <c r="A5" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -491,8 +560,8 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>920002</v>
+      <c r="A6" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -502,8 +571,8 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>920003</v>
+      <c r="A7" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -513,8 +582,8 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>920004</v>
+      <c r="A8" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -524,8 +593,8 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>920005</v>
+      <c r="A9" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
@@ -535,83 +604,83 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A10">
-        <v>920006</v>
+      <c r="A10" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A11">
-        <v>920007</v>
+      <c r="A11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A12">
-        <v>920008</v>
+      <c r="A12" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A13">
-        <v>920009</v>
+      <c r="A13" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A14">
-        <v>920010</v>
+      <c r="A14" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A15">
-        <v>920011</v>
+      <c r="A15" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A16">
-        <v>920012</v>
+      <c r="A16" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A17">
-        <v>920013</v>
+      <c r="A17" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A18">
-        <v>920014</v>
+      <c r="A18" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A19">
-        <v>920015</v>
+      <c r="A19" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A20">
-        <v>920016</v>
+      <c r="A20" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A21">
-        <v>920017</v>
+      <c r="A21" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A22">
-        <v>920018</v>
+      <c r="A22" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A23">
-        <v>920019</v>
+      <c r="A23" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A24">
-        <v>920020</v>
+      <c r="A24" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A25">
-        <v>920021</v>
+      <c r="A25" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/language/lang_item.xlsx
+++ b/Config/Excel/language/lang_item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20379"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProjects\Project001\Config\Excel\language\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project001\Config\Excel\language\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38CD696-71BE-4C50-A688-6604848A8DDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D86CF1-2A17-443A-872A-38C3FA619FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29865" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lang_system" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -30,13 +30,7 @@
     <t>text</t>
   </si>
   <si>
-    <t>color</t>
-  </si>
-  <si>
     <t>c</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t>string</t>
@@ -497,190 +491,163 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.625" customWidth="1"/>
-    <col min="2" max="2" width="37.25" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="37.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A25" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -693,22 +660,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -721,7 +688,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
